--- a/results/GSEA_POP_vs_Chen2006_convergent_pathways.xlsx
+++ b/results/GSEA_POP_vs_Chen2006_convergent_pathways.xlsx
@@ -14,13 +14,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction_all_panels" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Correction_pathways_in_common" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2006_GO_corrected" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2006_60genes_added" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2006_still_unmapped" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chen2006_POP_GO_common_60genes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POP_top_KEGG_for_reference" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concord36genes_GO_fixed" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concord36genes_KEGG_fixed" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'POP_GSEA_KEGG_results'!$A$1:$G$219</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chen2006_KEGG_ORA_corrected'!$A$1:$H$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correction_all_panels'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Correction_pathways_in_common'!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Chen2006_GO_corrected'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Chen2006_GO_corrected'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Chen2006_60genes_added'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Chen2006_still_unmapped'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Chen2006_POP_GO_common_60genes'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'POP_top_KEGG_for_reference'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Concord36genes_GO_fixed'!$A$1:$E$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Concord36genes_KEGG_fixed'!$A$1:$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -656,14 +668,3358 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>7) Follow-up: using the fuller 79-gene table and GO/KEGG (not GSEA) for the microarray side</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>You asked directly: are there really no shared pathways, even with GO and KEGG instead of GSEA, for the microarray comparison - using the 79 genes? Two things were done to answer this properly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="109" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>First, the candidate gene list was expanded: the original curation kept 58 of the paper's 79 genes, excluding 21 as unmappable 2003-2005-era entries (old KIAA IDs, unnamed hypothetical proteins). Re-examining those 21 found 2 more that CAN be mapped with confidence - LRRC32 (the classic older name for this gene was literally 'T-cell activation leucine repeat-rich protein') and LARGE1 ('like-glycosyltransferase' was LARGE's own historical description) - see the 'Chen2006_60genes_added' tab. The other 19 remain genuinely unmappable without a live gene database lookup (unavailable here) - see 'Chen2006_still_unmapped'. Guessing at those would risk introducing wrong genes, so they stay out. The panel is now 60 genes (34 up / 26 down), not 58.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Second, GO BP and KEGG ORA (not GSEA) were re-run on this 60-gene panel with the corrected universe (section 5), and directly compared against the POP (GSE53868) DEG-based GO/KEGG (534 DEGs, correct universe throughout, unaffected by the bug) - the same 'pathways significant in both, independently computed' comparison used before, now with the fullest gene list available and both ORA methods, not just GSEA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="49" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Answer: still only 1 GO BP term in common - 'response to lipopolysaccharide' (Chen 2006 side: DIO2/PTGER2/S100A7/CLDN1; POP side: DUSP10/EPO/F2R/FMO1/FOSL2/PTGS2/SELE/SLPI/SOD2/THBD/TRIB1) - and ZERO KEGG pathways in common, even with the 2 extra genes and testing GO and KEGG both. See 'Chen2006_POP_GO_common_60genes'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="214" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Why this genuinely happens (not a flaw in the check): POP's own DEG list is large (534 genes), so its own top enriched KEGG pathways (ECM-receptor interaction, cytokine-cytokine receptor interaction, MAPK signaling, hematopoietic cell lineage, TGF-beta signaling - see 'POP_top_KEGG_for_reference') are broad tissue-remodeling/immune themes that mathematically dominate a 534-gene enrichment run. Chen 2006's panel is tiny (60 genes) and specific, so KEGG (which needs a reasonably sized hit count per pathway to reach significance) finds nothing significant for it at all - not because the biology disagrees, but because a 60-gene list is too small to clear the KEGG bar on its own, no matter which 60 genes they are. This does NOT mean the keratin genes (KRT14/16/17, S100A7, TP63, PKP1, CLDN1) aren't shared - they ARE individually present among POP's 534 DEGs, as already shown in the direction-concordance crossing (35-45 shared genes, binomial p=0.018/2e-6). What's absent here is a specific difference: whether the same NAMED pathway independently tops BOTH lists when each is analyzed on its own, which is a much stricter and less informative question than 'are the actual genes shared.' The gene-level crossing remains the strongest, most direct evidence in this project - this pathway-label check is a secondary, harder-to-pass confirmation, and its negative result here is expected given the size mismatch between the two panels, not a sign that the keratinization finding is wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>8) The clearest, most direct answer: GO/KEGG on the 36 genes that are ACTUALLY shared</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="94" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>There is a better way to answer "are there shared pathways" than comparing two independently-computed top-pathway lists: run GO/KEGG directly on the 36 genes that Chen 2006 and the POP microarray actually agree on (the direction-concordant set from the earlier crossing) - the same-name-in-both-lists check in section 7 above is a weaker, indirect proxy for this. This ALSO turned out to have the same universe bug (it used the same wrong 191,076 background), so it was corrected too, using the real GSE53868 array gene list (31,072 genes) as universe, matching how the POP-alone analysis was always computed correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="79" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Corrected result: GO BP - 118 of 243 terms significant at FDR&lt;0.05, still topped by the same keratinization signature: intermediate filament bundle assembly (KRT14/PKP1), intermediate filament organization (KRT17/KRT14/KRT16), keratinocyte differentiation (KRT14/KRT16/S100A7), epidermis development, hair cycle, epithelial cell differentiation - see 'Concord36genes_GO_fixed'. KEGG - 0 of 37 pathways significant at FDR&lt;0.05 (was wrongly reported as 37 of 37 with the buggy universe) - see 'Concord36genes_KEGG_fixed'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="94" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>So: yes, GO does find shared, keratinization-specific pathway enrichment when tested on the actual overlapping genes (this is real and now correctly quantified, not the inflated number from before). KEGG does not, on any version of this comparison tried here - not because the biology disagrees, but because KEGG's larger, coarser gene sets need more hit genes to reach significance than a 36-60-gene candidate panel can realistically supply. This is the honest, final answer: real and significant at the GO level, absent at the KEGG level, for every variant tried (panel-alone vs panel-alone, concordant genes vs whole background, GSEA vs ORA, 58 vs 60 candidate genes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>Scripts: R/analysis_GSEA_POP_vs_Chen2006_convergent_pathways.R and R/analysis_CORRECTED_universe_standalone_panels.R</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TERM_A</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Count_A</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>pvalue_A</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>p.adjust_A</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>geneID_A</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Count_B</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>pvalue_B</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>p.adjust_B</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>geneID_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>response to lipopolysaccharide</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>0.0007175653664154</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>0.0419775739353057</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>DIO2/PTGER2/S100A7/CLDN1</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>8.782780436083649e-06</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.0016160316002393</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>DUSP10/EPO/F2R/FMO1/FOSL2/PTGS2/SELE/SLPI/SOD2/THBD/TRIB1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TERM_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>pvalue</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>p.adjust</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>geneID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>5144</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>1.75355196247898e-06</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0.0001893836119477</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>COMP/CSF3/ICAM1/IL6/SDC2/SELE/TGFB2/THBS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>4010</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3.35606175372103e-05</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.0018122733470093</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>CACNA1G/DUSP10/DUSP14/DUSP5/DUSP8/FGF9/GADD45A/GADD45B/IL1R1/JUND/MAP3K8/NFATC2/NR4A1/NTF3/TGFB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>4640</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.0001284726719597</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.0046250161905509</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>CSF3/EPO/IL1R1/IL6/ITGA1/ITGB3/KIT/MME</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4350</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.0005325254922861</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.0143781882917254</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BMP8B/COMP/ID4/INHBA/LEFTY2/TGFB2/THBS4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4060</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.0009216271123279</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.0199071456262836</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>CCR2/CCR5/CSF3/EPO/FLT1/IL1R1/IL2RB/IL6/INHBA/KIT/TGFB2/TNFRSF12A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>4614</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.0023924267500105</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0417961368714148</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>CPA3/CTSG/MME</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>5410</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.0029136306715071</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.0417961368714148</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>IL6/ITGA1/ITGA7/ITGB3/LMNA/TGFB2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4512</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.0030960101386233</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.0417961368714148</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>COMP/ITGA1/ITGA7/ITGB3/SDC2/THBS4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TERM</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>pvalue</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>p.adjust</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>geneID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>intermediate filament bundle assembly</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>1.30225286998491e-05</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0.0031644744740633</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>KRT14/PKP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>intermediate filament organization</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>3.03548614039739e-05</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.00324240499189</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>KRT17/KRT14/KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>keratinocyte differentiation</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>4.00296912579015e-05</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.00324240499189</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>KRT14/KRT16/S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>epidermis development</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>8.062372040101739e-05</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.0041558300672223</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>KRT14/S100A7/COL17A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>hair cycle</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8.551090673297e-05</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.0041558300672223</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>KRT14/KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>epithelial cell differentiation</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.0001231265354726</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0049866246866423</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>KRT17/KRT14/KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>mast cell degranulation</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.0002703006057589</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.009383292457061</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B/S100A13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>response to lipopolysaccharide</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.0003835665801939</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.0116508348733899</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>DIO2/PTGER2/S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of gene expression</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.0008797691170605</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.0207195890414534</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>LRRC32/TLE1/DKK1/PKP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of Wnt signaling pathway</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.0009413506724807</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.0207195890414534</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>TLE1/DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>protein sumoylation</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.0009901743577184999</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.0207195890414534</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>UBE2I/SAE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of canonical NF-kappaB signal transduction</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.0010231895822939</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.0207195890414534</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>UBE2I/CASP1/S100A13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of DNA-templated transcription</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.0017719512169282</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C/UBE2I/TLE1/CHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>keratinization</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.0017981784157145</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>KRT17/KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of translation</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.0020711082556321</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>KRT17/CIRBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>farnesol catabolic process</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.0023158936572004</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of interleukin-1 alpha production</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.0023158936572004</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>IL1R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of granulocyte chemotaxis</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.0023158936572004</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>AIM2 inflammasome complex assembly</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.0023158936572004</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>regulation of lens fiber cell differentiation</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.0023158936572004</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.0281381079349851</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of mesodermal cell fate specification</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>signaling receptor ligand precursor processing</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of mRNA catabolic process</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>PKP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of cyclin-dependent protein kinase activity</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>regulation of dopaminergic neuron differentiation</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>lymphatic endothelial cell migration</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.0034718842535419</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>LGALS8</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>selenocysteine incorporation</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>DIO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of cGMP-mediated signaling</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>relaxation of vascular associated smooth muscle</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of heart induction by negative regulation of canonical Wnt signaling pathway</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Wnt signaling pathway involved in somitogenesis</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>cytokine precursor processing</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>mitotic DNA replication initiation</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>0.0046265725977712</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>adenylate cyclase-activating G protein-coupled receptor signaling pathway</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>0.0047972750819393</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>PTGER2/ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>regulation of receptor internalization</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>pattern recognition receptor signaling pathway</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>meiosis I</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>CKS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>osmosensory signaling pathway</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>hemidesmosome assembly</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>COL17A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of interleukin-1 alpha production</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>S100A13</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>keratinocyte migration</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>digestive system development</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>motor learning</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>regulation of transforming growth factor beta activation</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>LRRC32</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of interleukin-1-mediated signaling pathway</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>0.0057799601150397</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>IL1R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of canonical Wnt signaling pathway</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>0.0068571504490567</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>TLE1/DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of interleukin-18 production</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of kinase activity</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>regulation of monoatomic ion transport</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>FXYD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>icosanoid biosynthetic process</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>embryonic placenta morphogenesis</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>xenophagy</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LGALS8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>cellular detoxification of aldehyde</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of tau-protein kinase activity</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>0.0069320482289823</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>0.0311942170304204</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>DNA strand elongation involved in DNA replication</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>0.008082838361724101</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0.0332903342694742</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>response to nematode</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>0.008082838361724101</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0.0332903342694742</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>PTGER2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of hair follicle development</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0.008082838361724101</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0.0332903342694742</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>KRT17</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>synapse pruning</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>0.008082838361724101</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>0.0332903342694742</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of cardiac muscle cell differentiation</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>0.008082838361724101</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>0.0332903342694742</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of cell migration</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>0.0084160510508742</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>0.0340850067560406</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>NISCH/KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>heart valve development</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>0.0092323319338784</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0.0345147178451146</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>mitotic nuclear membrane reassembly</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>0.0092323319338784</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>0.0345147178451146</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>UBE2I</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>thyroid hormone metabolic process</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>0.0092323319338784</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0.0345147178451146</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>DIO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>daunorubicin metabolic process</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>0.0092323319338784</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>0.0345147178451146</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>doxorubicin metabolic process</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>0.0092323319338784</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>0.0345147178451146</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>G protein-coupled adenosine receptor signaling pathway</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>UTP biosynthetic process</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>CTP biosynthetic process</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>outer dynein arm assembly</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>NISCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>epithelial cell-cell adhesion</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>SERPINB8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of Wnt signaling pathway, planar cell polarity pathway</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>0.0103805303645501</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>0.0355277306843053</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>double-strand break repair via break-induced replication</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>endocardial cushion development</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>GTP biosynthetic process</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of protein processing</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>IL1R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>regulation of DNA-templated DNA replication initiation</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>nuclear export</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>UBE2I</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of tumor necrosis factor-mediated signaling pathway</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>0.011527435071335</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>0.0359123938760822</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>response to reactive oxygen species</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>0.0126730474703255</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>0.0380191424109765</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of protein sumoylation</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>0.0126730474703255</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>0.0380191424109765</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>SAE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of mast cell degranulation</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>0.0126730474703255</v>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>0.0380191424109765</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>regulation of apoptotic process</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" s="6" t="n">
+        <v>0.0129331623406314</v>
+      </c>
+      <c r="D83" s="6" t="n">
+        <v>0.0383263225460174</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>CASP1/NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>hormone biosynthetic process</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>0.013817368976107</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>0.0399799567121933</v>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DIO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of transcription by RNA polymerase II</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>0.013820231949894</v>
+      </c>
+      <c r="D85" s="6" t="n">
+        <v>0.0399799567121933</v>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C/UBE2I/DKK1/CHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>endoderm formation</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>0.0149604010017622</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>0.0408469375666092</v>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>regulation of exit from mitosis</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>0.0149604010017622</v>
+      </c>
+      <c r="D87" s="6" t="n">
+        <v>0.0408469375666092</v>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>cellular response to extracellular stimulus</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>0.0149604010017622</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>0.0408469375666092</v>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>regulation of cell fate specification</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>0.0149604010017622</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>0.0408469375666092</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>CHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>genomic imprinting</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>0.0149604010017622</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>0.0408469375666092</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>thyroid hormone generation</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>0.0161021449588741</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>0.041625757712834</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>DIO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>spindle organization</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>0.0161021449588741</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>0.041625757712834</v>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>CHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>neuron maturation</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>0.0161021449588741</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>0.041625757712834</v>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of activated T cell proliferation</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>0.0161021449588741</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0.041625757712834</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>LRRC32</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>secondary palate development</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>0.0161021449588741</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>0.041625757712834</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>LRRC32</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of T cell chemotaxis</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>0.0172426022575244</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0.043195385036891</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of phosphorylation</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>0.0172426022575244</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>0.043195385036891</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>cellular response to organic substance</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>0.0172426022575244</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>0.043195385036891</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>peptide antigen assembly with MHC class II protein complex</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>0.0183817743062967</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>0.0442254569943575</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of DNA binding</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>0.0183817743062967</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>0.0442254569943575</v>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>uterus development</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>0.0183817743062967</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>0.0442254569943575</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>cellular response to prostaglandin E stimulus</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>0.0183817743062967</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>0.0442254569943575</v>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>PTGER2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>morphogenesis of an epithelium</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>0.019519662512279</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>0.0451740760998457</v>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>KRT16</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>positive regulation of monocyte chemotaxis</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>0.019519662512279</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>0.0451740760998457</v>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>S100A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>regulation of sodium ion transmembrane transporter activity</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>0.019519662512279</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>0.0451740760998457</v>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>FXYD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>regulation of stem cell differentiation</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>0.019519662512279</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>0.0451740760998457</v>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>CHD3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>regulation of neuron apoptotic process</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>0.0206562682810618</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>mitotic cell cycle phase transition</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>0.0206562682810618</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>CKS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>pyroptosis</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>0.0206562682810618</v>
+      </c>
+      <c r="D109" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of anoikis</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>0.0206562682810618</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>TLE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>DNA unwinding involved in DNA replication</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D111" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>cGMP-mediated signaling</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of ossification</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D113" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of peptidyl-serine phosphorylation</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>DKK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of cyclin-dependent protein serine/threonine kinase activity</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D115" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="inlineStr">
+        <is>
+          <t>negative regulation of mitotic cell cycle</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>0.0217915930167443</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>0.0460465835049466</v>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr">
+        <is>
+          <t>myeloid cell differentiation</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>0.0229256381219318</v>
+      </c>
+      <c r="D117" s="6" t="n">
+        <v>0.0480252591692193</v>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="inlineStr">
+        <is>
+          <t>DNA metabolic process</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>0.0240584049977406</v>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>0.0495440035122963</v>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>NME1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t>Rac protein signal transduction</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>0.0240584049977406</v>
+      </c>
+      <c r="D119" s="6" t="n">
+        <v>0.0495440035122963</v>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>NISCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E119"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>TERM_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>pvalue</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>p.adjust</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>geneID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>4640</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>0.0045895473373063</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0.10717603356384</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>IL1R2/HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>4110</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>0.0077488110108904</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.10717603356384</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>CDKN1C/MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>4120</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.0086899486673383</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.10717603356384</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>UBE2I/SAE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>650</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.0285767181774083</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>591</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.030828241710667</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5310</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.0341960170061346</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4080</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.0351965049647804</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>PTGER2/ADORA2B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>3030</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.0353160783226659</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>MCM4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0.0375524135939262</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>AKR1B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>5330</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.0420099733715231</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>5332</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.044231219929188</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>4940</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.0486587013349181</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>4621</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.0508649580939904</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>4623</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.0508649580939904</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>5320</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.05306624012573</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>4672</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.0541650190251812</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>5014</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.0552625583274988</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>CASP1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>5150</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.0563588593912323</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.115848766526422</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>5322</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.0596403467147641</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.116141727812962</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>5140</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.0737323789563518</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.132399063144971</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>HLA-DRB4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8390,14 +11746,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Chen 2006 (58 genes, SUI secretory phase)</t>
+          <t>Chen 2006 (60 genes, SUI secretory phase - expanded from 58)</t>
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>76</v>
@@ -8569,7 +11925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8616,10 +11972,10 @@
         <v>4</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3.83202099439257e-05</v>
+        <v>4.41539481558637e-05</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.0129774084850186</v>
+        <v>0.015641656494565</v>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
@@ -8630,63 +11986,63 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>establishment of skin barrier</t>
+          <t>positive regulation of cGMP-mediated signaling</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>0.0001201539398974</v>
+        <v>0.0001334305278774</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>0.0129774084850186</v>
+        <v>0.015641656494565</v>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>KRT16/TP63/CLDN1</t>
+          <t>ADORA2B/NPR1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>positive regulation of cGMP-mediated signaling</t>
+          <t>intermediate filament bundle assembly</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>0.0001241857271293</v>
+        <v>0.0001334305278774</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.0129774084850186</v>
+        <v>0.015641656494565</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>ADORA2B/NPR1</t>
+          <t>KRT14/PKP1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>intermediate filament bundle assembly</t>
+          <t>establishment of skin barrier</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.0001241857271293</v>
+        <v>0.0001336893717484</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>0.0129774084850186</v>
+        <v>0.015641656494565</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>KRT14/PKP1</t>
+          <t>KRT16/TP63/CLDN1</t>
         </is>
       </c>
     </row>
@@ -8700,10 +12056,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.0005231029858811</v>
+        <v>0.0005810674638764</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0380594693392875</v>
+        <v>0.0419775739353057</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
@@ -8714,47 +12070,249 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>response to lipopolysaccharide</t>
+          <t>hair cycle</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.0006263698086503</v>
+        <v>0.0006844684414360999</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.0380594693392875</v>
+        <v>0.0419775739353057</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>DIO2/PTGER2/S100A7/CLDN1</t>
+          <t>KRT14/KRT16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>hair cycle</t>
+          <t>skeletal muscle tissue regeneration</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.0006373595343898999</v>
+        <v>0.0006844684414360999</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.0380594693392875</v>
+        <v>0.0419775739353057</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>KRT14/KRT16</t>
+          <t>SGCA/LARGE1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>response to lipopolysaccharide</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.0007175653664154</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.0419775739353057</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>DIO2/PTGER2/S100A7/CLDN1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:E9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ProbeSet</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>GeneDescription</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>GeneSymbol</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Confidence_note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>212978</v>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>T-cell activation leucine repeat-rich protein</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>LRRC32</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Classic older name for LRRC32/GARP (Glycoprotein A Repetitions Predominant) - confident mapping</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>215543</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Like-glycosyltransferase</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>LARGE1</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>LARGE (now LARGE1) was historically annotated exactly as 'like-glycosyltransferase' - confident mapping</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>ProbeSet</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Why_excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>203712, 204175, 215846, 220980 (Table II)</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Minor histocompatibility antigen HA-8 / unnamed zinc finger protein / weak-similarity hypothetical / hypothetical DKFZp434B195 - no reliable current symbol without a live database lookup, which is unavailable in this environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>204589, 208476, 209981, 210276, 211986, 212669, 212778, 214258, 219560, 220940, 221123, 221203 (Table III)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Old KIAA IDs and hypothetical-protein entries (FLJ#####, MGC5395) from 2003-2005 nomenclature, plus one garbled/truncated table cell ('Gamma') - guessing at these would risk introducing wrong genes into the analysis, so left out rather than fabricated</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>205903 (Table III)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Duplicate probe for KCNN3 (same gene as 205902, already included) - not a loss of information</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>